--- a/信吾/添付ファイル/信吾のインターン線表.xlsx
+++ b/信吾/添付ファイル/信吾のインターン線表.xlsx
@@ -89,6 +89,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
@@ -99,17 +104,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,28 +178,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -576,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -664,7 +661,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>りそな銀行（マーケット部門）</t>
+          <t>りそな銀行（総合職）</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -674,16 +671,16 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>インターン実施済。GWで財務諸表を読めるのは信吾だけという強みを発揮。応募月の記録なし、結果月は推定（夏）</t>
+          <t>2026年7月にインターン実施済・合格。GWで財務諸表を読めるのは信吾だけという強みを発揮。マーケット部門のインターン合格が決定</t>
         </is>
       </c>
       <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>合格</t>
         </is>
       </c>
+      <c r="G4" s="8" t="n"/>
       <c r="H4" s="10" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
@@ -728,7 +725,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>合格発表 2026/08/10</t>
+          <t>2026年8月にインターン実施済・合格（合格発表 2026/08/10）</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -776,27 +773,27 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>みずほ信託銀行</t>
+          <t>日本政策金融公庫</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>選考中</t>
+          <t>合格</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>ES・玉手箱は合格、GD実施済み、結果待ち（2026/09/18時点）</t>
+          <t>2026年8月にインターン実施済・合格</t>
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>結果待ち</t>
-        </is>
-      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n"/>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
@@ -805,7 +802,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>NTTファイナンス</t>
+          <t>みずほ信託銀行</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -815,17 +812,17 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>8月提出予定インターン。ES選考で不合格</t>
+          <t>ES・玉手箱は合格、GD実施後、AI面接で不合格。結果月は不明のため判明時点(2026/09/19)近辺の9月と推定</t>
         </is>
       </c>
       <c r="E9" s="13" t="n"/>
       <c r="F9" s="13" t="n"/>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>不合格</t>
         </is>
       </c>
-      <c r="H9" s="14" t="n"/>
       <c r="I9" s="13" t="n"/>
       <c r="J9" s="13" t="n"/>
       <c r="K9" s="13" t="n"/>
@@ -834,7 +831,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>KPMGコンサル</t>
+          <t>NTTファイナンス</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -844,7 +841,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>ES・玉手箱は合格。ケース面接後、不合格通知 2026/08/07</t>
+          <t>8月提出予定インターン。ES選考で不合格</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -863,7 +860,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>横浜銀行（秋インターン）</t>
+          <t>KPMGコンサル</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -873,17 +870,17 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>ES・適性検査は合格、AI面接で不合格。秋インターンのため9月と推定</t>
+          <t>ES・玉手箱は合格。ケース面接後、不合格通知 2026/08/07</t>
         </is>
       </c>
       <c r="E11" s="13" t="n"/>
       <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>不合格</t>
         </is>
       </c>
+      <c r="H11" s="14" t="n"/>
       <c r="I11" s="13" t="n"/>
       <c r="J11" s="13" t="n"/>
       <c r="K11" s="13" t="n"/>
@@ -892,7 +889,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>みずほ（秋インターン）</t>
+          <t>横浜銀行（秋インターン）</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -902,13 +899,13 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>みずほ信託銀行とは別枠。2026/09/18時点で不合格判明</t>
+          <t>ES・適性検査は合格、AI面接で不合格。秋インターンのため9月と推定</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>不合格</t>
         </is>
@@ -921,7 +918,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>農林中央金庫（秋インターン）</t>
+          <t>みずほ（秋インターン）</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
@@ -931,13 +928,13 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>2026/09/18時点で不合格判明</t>
+          <t>みずほ信託銀行とは別枠。2026/09/18時点で不合格判明</t>
         </is>
       </c>
       <c r="E13" s="13" t="n"/>
       <c r="F13" s="13" t="n"/>
       <c r="G13" s="13" t="n"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>不合格</t>
         </is>
@@ -950,17 +947,17 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>かんぽ</t>
+          <t>農林中央金庫（秋インターン）</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>選考中</t>
+          <t>不合格</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>応募済み、結果待ち（合否まちインターン）</t>
+          <t>2026/09/18時点で不合格判明</t>
         </is>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -968,7 +965,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>結果待ち</t>
+          <t>不合格</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -979,7 +976,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>JERA</t>
+          <t>かんぽ</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -995,7 +992,7 @@
       <c r="E15" s="13" t="n"/>
       <c r="F15" s="13" t="n"/>
       <c r="G15" s="13" t="n"/>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>結果待ち</t>
         </is>
@@ -1008,7 +1005,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>クニエ</t>
+          <t>JERA</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1018,17 +1015,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>8月提出予定だった。結果は未記録</t>
+          <t>応募済み、結果待ち（合否まちインターン）</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>応募</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>結果待ち</t>
+        </is>
+      </c>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
@@ -1037,31 +1034,31 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>日本政策金融公庫</t>
+          <t>デロイトトーマツFAS</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>選考中</t>
+          <t>応募予定</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>8月提出予定だった。結果は未記録</t>
+          <t>秋インターンに応募予定。具体的な提出月は未定</t>
         </is>
       </c>
       <c r="E17" s="13" t="n"/>
       <c r="F17" s="13" t="n"/>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>応募</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>予定</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="19" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -1082,15 +1079,15 @@
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>予定</t>
         </is>
       </c>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="20" t="n"/>
-      <c r="L18" s="20" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -1111,47 +1108,18 @@
       <c r="E19" s="13" t="n"/>
       <c r="F19" s="13" t="n"/>
       <c r="G19" s="13" t="n"/>
-      <c r="H19" s="19" t="inlineStr">
+      <c r="H19" s="18" t="inlineStr">
         <is>
           <t>予定</t>
         </is>
       </c>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="20" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>NTTドコモ</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>応募予定</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>秋以降提出予定。具体的な提出月は未定</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>予定</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="20" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="19" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>※応募月・結果月ともに正確な日付の記録がないものは推定または空欄にしています。赤枠は本日（2026/09/19）時点の月（2026年9月）を示します。</t>
         </is>
@@ -1160,7 +1128,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="E1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
